--- a/data/content-review-batches/15_rows_141-150.xlsx
+++ b/data/content-review-batches/15_rows_141-150.xlsx
@@ -389,20 +389,16 @@
       <x:c r="I2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">אופן ההכנה
-1.	מכינים את התחתית
-מרסקים את הביסקוויטים לחתיכות יחסית גדולות, כדי שיישארו צ’אנקים טעימים בביס.
+1.	מכינים את התחתית: מרסקים את הביסקוויטים לחתיכות יחסית גדולות, כדי שיישארו צ’אנקים טעימים בביס.
 במקביל, ממיסים את השוקולד הלבן, החמאה והחלב בקלחת או במיקרו, עד שהתערובת חלקה לגמרי.
 שופכים את התערובת על הביסקוויטים, מערבבים היטב ומעבירים לתבנית בקוטר 22.
 מהדקים ומיישרים את התערובת לתחתית, ומעבירים למקרר בינתיים.
-2.	מכינים את הקרם
-את השמנת המתוקה עם הסוכר במשך 2 דקות.
+2.	מכינים את הקרם: מקציפים את השמנת המתוקה עם הסוכר במשך 2 דקות.
 מוסיפים את גבינת המסקרפונה ואת האינסטנט פודינג, וממשיכים להקציף עד לקבלת קרם יציב.
 מורחים את הקרם על תחתית הביסקוויטים שבתבנית.
-3.	מכינים את הגנאש
-ממיסים במיקרו את השוקולד הלבן יחד עם השמנת המתוקה.
+3.	מכינים את הגנאש: ממיסים במיקרו את השוקולד הלבן יחד עם השמנת המתוקה.
 כשהגנאש מתקרר מעט, שופכים אותו על העוגה ומיישרים בעדינות.
-4.	הקירור (שלב חשוב!)
-נותנים לעוגה להתייצב לילה שלם במקרר – ועדיף אפילו 24 שעות.
+4.	הקירור (שלב חשוב!): נותנים לעוגה להתייצב לילה שלם במקרר – ועדיף אפילו 24 שעות.
 המרקם והטעם משתדרגים ככל שהיא נחה.
 בתאבון מחכה לשמוע איך יצא 🩷🩷</x:t>
         </x:is>
@@ -491,29 +487,25 @@
       </x:c>
       <x:c r="I3" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">אופן הכנת הבצק:
-בקערת מיקסר עם וו לישה שמים קמח, שמרים וסוכר ומערבבים דקה (אפשר גם בכף)
+          <x:t xml:space="preserve">אופן הכנת הבצק: בקערת מיקסר עם וו לישה שמים קמח, שמרים וסוכר ומערבבים דקה (אפשר גם בכף)
 מוסיפים את הביצים והמים ולשים עד שהבצק מתחיל להתאחד
 לאחר מכן מוסיפים את הנטורינה בהדרגה – קובייה אחר קובייה עד שהיא נטמעת לגמרי
 אחרי שכל הנטורינה נטמעה לשים עוד 5 דקות ואז מוסיפים את המלח ולשים עוד כמה דקות עד שמתיימרת לנו רשת גלוטן
 מעבירים לקערה משומנת, מכסים ומניחים להתפחה כשעה־שעה וחצי, עד שהבצק מכפיל את עצמו.
-אופן הכנת המילוי:
-ממיסים במיקרו את השוקולד המריר והנטורינה בפולסים קצרים עד שהתערובת חלקה.
+אופן הכנת המילוי: ממיסים במיקרו את השוקולד המריר והנטורינה בפולסים קצרים עד שהתערובת חלקה.
 מוסיפים את הסוכר ומנפים פנימה את הקקאו, מערבבים היטב עד למשחה אחידה.
 מומלץ לחמם קצת את צנצנת הנוטלה במיקרו או בקערה עם מים חמים כדי שתהיה רכה ונוחה למריחה.
-הרכבה:
-לאחר שהבצק תפח, מחלקים אותו לשני חלקים שווים.
+הרכבה: לאחר שהבצק תפח, מחלקים אותו לשני חלקים שווים.
 מרדדים את החלק הראשון למלבן.
 על חצי מהמלבן מורחים שכבת מילוי שוקולד, סוגרים את הבצק, ומרדדים שוב דק דק.
 מורחים שכבת נוטלה דקה, מגלגלים לרולדה וחותכים לאורכה ליצירת צורת בורג.
 מעצבים ומניחים בתבנית מרופדת בנייר אפייה.
 מתפיחים שוב כחצי שעה.
 אופים בתנור שחומם ל־170 מעלות למשך 35–45 דקות עד שהעוגה זהובה ומפיצה ריח מטריף.
-מי סוכר:
-שופכים מים רותחים על הסוכר ומערבבים עד שהסוכר נמס לגמרי
+מי סוכר: שופכים מים רותחים על הסוכר ומערבבים עד שהסוכר נמס לגמרי
 כשהעוגה יוצאת מהתנור, מיד מורחים אותה במי סוכר בעדינות (מומלץ למזוג מי סוכר קרים על עוגה חמה)
 לא חותכים את העוגה כשהיא חמה – נותנים לה להתקרר לפחות חצי שעה כדי שתתייצב ותישאר רכה ולחה מבפנים.
-וזהו בתאבון תספרו לי איך יצא ❤️❤️ 
+וזהו בתאבון תספרו לי איך יצא ❤️❤️
 בשיתוף ממומן נוטלה @nutella.israel</x:t>
         </x:is>
       </x:c>
